--- a/KatalonData/Bootstrap/VT-Misc-Data.xlsx
+++ b/KatalonData/Bootstrap/VT-Misc-Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\Bootstrap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8B7FB720-3811-46BB-AC5D-AB6CE5EB12DB}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{9043DBE8-F1FD-4977-A8FD-F436180587D4}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="2" firstSheet="1" tabRatio="899" windowHeight="10420" windowWidth="19420" xWindow="-110" xr2:uid="{F4488FFE-6E25-4FE6-A3E4-075D849B89C6}" yWindow="-110"/>
+    <workbookView activeTab="9" tabRatio="899" windowHeight="15675" windowWidth="28996" xWindow="-98" xr2:uid="{F4488FFE-6E25-4FE6-A3E4-075D849B89C6}" yWindow="-98"/>
   </bookViews>
   <sheets>
     <sheet name="Sale-EncryptedUDF" r:id="rId1" sheetId="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="279">
   <si>
     <t>Result</t>
   </si>
@@ -157,9 +157,6 @@
     <t>12</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>36 Cornor Road</t>
   </si>
   <si>
@@ -718,108 +715,6 @@
     <t>Do Not Run</t>
   </si>
   <si>
-    <t>Tue Aug 19 18:45:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:45:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:46:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:46:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:47:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:48:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:48:54 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:49:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:50:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:50:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:51:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:52:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:52:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:53:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:54:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:54:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 18:55:22 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:29:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:30:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:31:27 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:32:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:33:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:33:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:34:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:35:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:36:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:37:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:38:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:39:02 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:39:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:40:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:41:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:42:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Tue Aug 19 19:43:15 EDT 2025</t>
-  </si>
-  <si>
     <t>Tue Aug 19 19:44:06 EDT 2025</t>
   </si>
   <si>
@@ -829,109 +724,163 @@
     <t>Phone Number is disabled in QA</t>
   </si>
   <si>
+    <t>Fri Nov 14 21:58:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 21:59:25 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:00:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:00:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:01:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:02:23 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:03:07 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:03:49 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:04:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:05:17 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:06:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:06:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:07:25 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:08:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:08:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:09:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:10:15 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:10:57 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:11:52 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:12:46 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:13:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:14:37 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:15:32 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:16:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:17:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:18:15 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:19:10 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:20:06 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:21:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:21:54 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:22:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:23:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:24:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Nov 14 22:25:33 EST 2025</t>
+  </si>
+  <si>
+    <t>2028</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Fri Nov 14 21:58:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 21:59:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:00:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:00:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:01:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:02:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:03:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:03:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:04:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:05:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:06:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:06:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:07:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:08:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:08:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:09:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:10:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:10:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:11:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:12:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:13:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:14:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:15:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:16:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:17:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:18:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:19:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:20:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:21:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:21:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:22:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:23:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:24:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 14 22:25:33 EST 2025</t>
+    <t>Tue Jan 20 19:53:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:54:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:55:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:55:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:56:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:57:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:58:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:59:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 19:59:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:00:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:01:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:02:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:03:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:03:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:04:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:05:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jan 20 20:06:16 EST 2026</t>
   </si>
 </sst>
 </file>
@@ -1320,24 +1269,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03923135-EB1A-448D-835E-7A1175975924}">
   <dimension ref="A1:AG3"/>
-  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="4" style="1" width="12.1796875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.453125" collapsed="true"/>
-    <col min="6" max="7" customWidth="true" style="1" width="30.1796875" collapsed="true"/>
+    <col min="1" max="4" style="1" width="12.19921875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
+    <col min="6" max="7" customWidth="true" style="1" width="30.19921875" collapsed="true"/>
     <col min="8" max="8" customWidth="true" style="1" width="22.0" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="30.54296875" collapsed="true"/>
-    <col min="11" max="13" style="1" width="12.1796875" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="24.453125" collapsed="true"/>
-    <col min="15" max="29" style="1" width="12.1796875" collapsed="true"/>
-    <col min="30" max="30" customWidth="true" style="1" width="20.453125" collapsed="true"/>
-    <col min="31" max="31" style="1" width="12.1796875" collapsed="true"/>
-    <col min="32" max="32" customWidth="true" style="1" width="24.7265625" collapsed="true"/>
-    <col min="33" max="16384" style="1" width="12.1796875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="15.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="30.53125" collapsed="true"/>
+    <col min="11" max="13" style="1" width="12.19921875" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="15" max="29" style="1" width="12.19921875" collapsed="true"/>
+    <col min="30" max="30" customWidth="true" style="1" width="20.46484375" collapsed="true"/>
+    <col min="31" max="31" style="1" width="12.19921875" collapsed="true"/>
+    <col min="32" max="32" customWidth="true" style="1" width="24.73046875" collapsed="true"/>
+    <col min="33" max="16384" style="1" width="12.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1357,7 +1306,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1435,18 +1384,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>32</v>
@@ -1464,78 +1413,78 @@
         <v>36</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AF2" s="1" t="s">
-        <v>54</v>
-      </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>34</v>
@@ -1547,58 +1496,58 @@
         <v>36</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AE3" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="AF3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1612,20 +1561,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0D2A2F-57A5-4477-9C97-296B6400B44D}">
   <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="4" style="1" width="12.1796875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="34.54296875" collapsed="true"/>
+    <col min="1" max="4" style="1" width="12.19921875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="34.53125" collapsed="true"/>
     <col min="7" max="7" customWidth="true" style="1" width="22.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="30.54296875" collapsed="true"/>
-    <col min="10" max="12" style="1" width="12.1796875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="24.453125" collapsed="true"/>
-    <col min="14" max="16384" style="1" width="12.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="15.53125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="30.53125" collapsed="true"/>
+    <col min="10" max="12" style="1" width="12.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="12.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,24 +1630,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>35</v>
@@ -1707,39 +1656,39 @@
         <v>36</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>41</v>
-      </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>35</v>
@@ -1748,19 +1697,19 @@
         <v>36</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1774,48 +1723,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3D0227F-6E51-424B-BFCC-C4083DCC9ECD}">
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.1796875" defaultRowHeight="19.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.19921875" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.1796875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.19921875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="6.265625" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="31.81640625" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="28.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="32.54296875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.26953125" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.81640625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="4.26953125" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="7.54296875" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.453125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="31.796875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="28.73046875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="32.53125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.265625" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.796875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="4.265625" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="7.53125" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.46484375" collapsed="true"/>
     <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
     <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="6.0" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="5.81640625" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="8.81640625" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="5.796875" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.73046875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
     <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="7.26953125" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="7.265625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="7.81640625" collapsed="true"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="7.796875" collapsed="true"/>
     <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.453125" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="6.81640625" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="16.7265625" collapsed="true"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="5.453125" collapsed="true"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.7265625" collapsed="true"/>
-    <col min="36" max="36" customWidth="true" style="1" width="18.453125" collapsed="true"/>
-    <col min="37" max="16384" style="1" width="12.1796875" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="6.796875" collapsed="true"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="5.46484375" collapsed="true"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
+    <col min="36" max="36" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="37" max="16384" style="1" width="12.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="19.5" r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="1" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1829,22 +1778,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>6</v>
@@ -1922,30 +1871,30 @@
         <v>30</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>32</v>
@@ -1963,90 +1912,90 @@
         <v>36</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AI2" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="AJ2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>34</v>
@@ -2058,84 +2007,84 @@
         <v>36</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AH3" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="AI3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>32</v>
@@ -2144,7 +2093,7 @@
         <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>35</v>
@@ -2153,93 +2102,93 @@
         <v>36</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AH4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AH4" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="AI4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="K5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>35</v>
@@ -2248,84 +2197,84 @@
         <v>36</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG5" s="1" t="s">
+      <c r="AH5" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AH5" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="AI5" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
-    <row ht="14.5" r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row ht="14.25" r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>32</v>
@@ -2334,7 +2283,7 @@
         <v>33</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>35</v>
@@ -2343,93 +2292,93 @@
         <v>36</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG6" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG6" s="1" t="s">
+      <c r="AH6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AH6" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="AI6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
-    <row ht="14.5" r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row ht="14.25" r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="K7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>35</v>
@@ -2438,61 +2387,61 @@
         <v>36</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG7" s="1" t="s">
+      <c r="AH7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AH7" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="AI7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2507,49 +2456,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55730CF5-7BB7-4109-818A-846914C1A1E6}">
   <dimension ref="A1:AL6"/>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.1796875" defaultRowHeight="19.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.19921875" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.7265625" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="31.81640625" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="28.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="32.54296875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.26953125" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.81640625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="4.26953125" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="7.54296875" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.453125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="31.796875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="28.73046875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="32.53125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.265625" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.796875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="4.265625" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="7.53125" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.46484375" collapsed="true"/>
     <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
     <col min="19" max="19" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="20" max="20" customWidth="true" style="1" width="27.7265625" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="8.81640625" collapsed="true"/>
+    <col min="20" max="20" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="6.73046875" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
     <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="7.26953125" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="7.265625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="7.81640625" collapsed="true"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="7.796875" collapsed="true"/>
     <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.453125" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="6.81640625" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="16.7265625" collapsed="true"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="5.453125" collapsed="true"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.7265625" collapsed="true"/>
-    <col min="36" max="36" customWidth="true" style="1" width="18.453125" collapsed="true"/>
-    <col min="37" max="37" customWidth="true" style="1" width="25.1796875" collapsed="true"/>
-    <col min="38" max="16384" style="1" width="12.1796875" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="6.796875" collapsed="true"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="5.46484375" collapsed="true"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.73046875" collapsed="true"/>
+    <col min="36" max="36" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="37" max="37" customWidth="true" style="1" width="25.19921875" collapsed="true"/>
+    <col min="38" max="16384" style="1" width="12.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="19.5" r="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2563,22 +2512,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>6</v>
@@ -2656,33 +2605,33 @@
         <v>30</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>32</v>
@@ -2700,96 +2649,96 @@
         <v>36</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AI2" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="AJ2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="3" spans="1:37" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>34</v>
@@ -2801,90 +2750,90 @@
         <v>36</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T3" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AH3" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="AI3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="4" spans="1:37" x14ac:dyDescent="0.45">
       <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>32</v>
@@ -2893,7 +2842,7 @@
         <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>35</v>
@@ -2902,99 +2851,99 @@
         <v>36</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="1" t="s">
+      <c r="AH4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG4" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="AK4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row customHeight="1" ht="19.5" r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row customHeight="1" ht="19.5" r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="K5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="M5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>35</v>
@@ -3003,93 +2952,93 @@
         <v>36</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" s="1" t="s">
+      <c r="AH5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG5" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="AK5" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
-    <row ht="58" r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row ht="42.75" r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="C6" s="1" t="s">
-        <v>260</v>
+        <v>225</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>32</v>
@@ -3107,70 +3056,71 @@
         <v>36</v>
       </c>
       <c r="P6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="U6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="V6" s="1" t="s">
+      <c r="W6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="Y6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AA6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AB6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB6" s="1" t="s">
+      <c r="AC6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AD6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AE6" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AE6" s="1" t="s">
+      <c r="AF6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AF6" s="1" t="s">
+      <c r="AG6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AG6" s="1" t="s">
+      <c r="AH6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AI6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AI6" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="AJ6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
@@ -3181,22 +3131,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A29DF0-E80A-4D1A-9523-089EBE8AD58D}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="25.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="25.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="5.1796875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="2" width="6.26953125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="5.19921875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="2" width="6.265625" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="2" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="2" width="9.1796875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="26.81640625" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="2" width="11.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="29.1796875" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="2" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="31.81640625" collapsed="true"/>
-    <col min="11" max="16384" style="2" width="25.81640625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="2" width="9.19921875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="26.796875" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="2" width="11.73046875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="29.19921875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="2" width="10.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="31.796875" collapsed="true"/>
+    <col min="11" max="16384" style="2" width="25.796875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3210,25 +3160,25 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3236,22 +3186,22 @@
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -3266,46 +3216,46 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CE1261-B725-4177-BF21-774BDC019B75}">
   <dimension ref="A1:AL19"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="26.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="20.26953125" collapsed="true"/>
-    <col min="4" max="4" style="2" width="9.1796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="10.81640625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="2" width="25.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="11.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="2" width="28.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="13.1796875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="32.26953125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="2" width="31.81640625" collapsed="true"/>
+    <col min="1" max="1" style="2" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="20.265625" collapsed="true"/>
+    <col min="4" max="4" style="2" width="9.19921875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="10.796875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="25.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="11.796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="2" width="28.53125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="2" width="13.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="2" width="32.265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="2" width="31.796875" collapsed="true"/>
     <col min="12" max="12" customWidth="true" style="2" width="18.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="2" width="20.7265625" collapsed="true"/>
-    <col min="14" max="16" style="2" width="9.1796875" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" style="2" width="28.1796875" collapsed="true"/>
-    <col min="18" max="19" style="2" width="9.1796875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="2" width="20.73046875" collapsed="true"/>
+    <col min="14" max="16" style="2" width="9.19921875" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="2" width="28.19921875" collapsed="true"/>
+    <col min="18" max="19" style="2" width="9.19921875" collapsed="true"/>
     <col min="20" max="20" customWidth="true" style="2" width="25.0" collapsed="true"/>
-    <col min="21" max="21" customWidth="true" style="2" width="22.26953125" collapsed="true"/>
-    <col min="22" max="22" style="2" width="9.1796875" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="2" width="17.7265625" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="2" width="15.54296875" collapsed="true"/>
+    <col min="21" max="21" customWidth="true" style="2" width="22.265625" collapsed="true"/>
+    <col min="22" max="22" style="2" width="9.19921875" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="2" width="17.73046875" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="2" width="15.53125" collapsed="true"/>
     <col min="25" max="25" customWidth="true" style="2" width="16.0" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="2" width="19.1796875" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="2" width="18.81640625" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="2" width="13.81640625" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="2" width="21.26953125" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="2" width="19.19921875" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="2" width="18.796875" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="2" width="13.796875" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="2" width="21.265625" collapsed="true"/>
     <col min="30" max="30" customWidth="true" style="2" width="22.0" collapsed="true"/>
-    <col min="31" max="31" customWidth="true" style="2" width="24.453125" collapsed="true"/>
-    <col min="32" max="32" customWidth="true" style="2" width="21.81640625" collapsed="true"/>
-    <col min="33" max="33" customWidth="true" style="2" width="18.7265625" collapsed="true"/>
-    <col min="34" max="34" style="2" width="9.1796875" collapsed="true"/>
-    <col min="35" max="35" customWidth="true" style="2" width="30.453125" collapsed="true"/>
-    <col min="36" max="36" customWidth="true" style="2" width="25.26953125" collapsed="true"/>
+    <col min="31" max="31" customWidth="true" style="2" width="24.46484375" collapsed="true"/>
+    <col min="32" max="32" customWidth="true" style="2" width="21.796875" collapsed="true"/>
+    <col min="33" max="33" customWidth="true" style="2" width="18.73046875" collapsed="true"/>
+    <col min="34" max="34" style="2" width="9.19921875" collapsed="true"/>
+    <col min="35" max="35" customWidth="true" style="2" width="30.46484375" collapsed="true"/>
+    <col min="36" max="36" customWidth="true" style="2" width="25.265625" collapsed="true"/>
     <col min="37" max="37" customWidth="true" style="2" width="26.0" collapsed="true"/>
-    <col min="38" max="16384" style="2" width="9.1796875" collapsed="true"/>
+    <col min="38" max="16384" style="2" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="1" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3319,22 +3269,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>6</v>
@@ -3412,15 +3362,15 @@
         <v>30</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
-    <row customFormat="1" r="2" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="2" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
         <v>262</v>
@@ -3429,25 +3379,25 @@
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>33</v>
@@ -3462,66 +3412,66 @@
         <v>36</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ2" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
-    <row customFormat="1" r="3" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="3" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
         <v>263</v>
@@ -3530,31 +3480,31 @@
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>35</v>
@@ -3563,66 +3513,66 @@
         <v>36</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" s="1" t="s">
+      <c r="V3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE3" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
-    <row customFormat="1" r="4" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="4" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
         <v>264</v>
@@ -3631,31 +3581,31 @@
         <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>35</v>
@@ -3664,69 +3614,69 @@
         <v>36</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="1" t="s">
+      <c r="V4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC4" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AD4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI4" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AJ4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AH4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>83</v>
-      </c>
     </row>
-    <row customFormat="1" r="5" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="5" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
         <v>265</v>
@@ -3735,31 +3685,31 @@
         <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>35</v>
@@ -3768,72 +3718,72 @@
         <v>36</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" t="s">
+        <v>133</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="T5" t="s">
-        <v>134</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AD5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD5" s="1" t="s">
+      <c r="AE5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI5" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF5" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG5" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ5" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AK5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
-    <row customFormat="1" r="6" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="6" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
         <v>266</v>
@@ -3842,28 +3792,28 @@
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>34</v>
@@ -3875,69 +3825,69 @@
         <v>36</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S6" s="1" t="s">
+      <c r="V6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="Y6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AA6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AD6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AE6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI6" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF6" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI6" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="AJ6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
-    <row customFormat="1" r="7" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="7" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
         <v>267</v>
@@ -3946,31 +3896,31 @@
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>35</v>
@@ -3979,69 +3929,69 @@
         <v>36</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S7" s="1" t="s">
+      <c r="V7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="AA7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AD7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD7" s="1" t="s">
+      <c r="AE7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE7" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row customFormat="1" r="8" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="8" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
         <v>268</v>
@@ -4050,31 +4000,31 @@
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>35</v>
@@ -4083,69 +4033,69 @@
         <v>36</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S8" s="1" t="s">
+      <c r="V8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W8" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W8" s="1" t="s">
+      <c r="X8" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="Y8" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Z8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="AA8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC8" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AD8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD8" s="1" t="s">
+      <c r="AE8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI8" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE8" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH8" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI8" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
-    <row customFormat="1" r="9" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="9" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
         <v>269</v>
@@ -4154,31 +4104,31 @@
         <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>35</v>
@@ -4187,69 +4137,69 @@
         <v>36</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S9" s="1" t="s">
+      <c r="V9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W9" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X9" s="1" t="s">
+      <c r="Y9" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Z9" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AA9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AD9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD9" s="1" t="s">
+      <c r="AE9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI9" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF9" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
-    <row customFormat="1" r="10" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="10" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
         <v>270</v>
@@ -4258,31 +4208,31 @@
         <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>35</v>
@@ -4291,69 +4241,69 @@
         <v>36</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S10" s="1" t="s">
+      <c r="V10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W10" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X10" s="1" t="s">
+      <c r="Y10" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="AA10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC10" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC10" s="1" t="s">
+      <c r="AD10" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD10" s="1" t="s">
+      <c r="AE10" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI10" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE10" s="1" t="s">
+      <c r="AJ10" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AF10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG10" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK10" s="1" t="s">
-        <v>112</v>
-      </c>
     </row>
-    <row customFormat="1" r="11" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="11" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
@@ -4362,31 +4312,31 @@
         <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>35</v>
@@ -4395,69 +4345,69 @@
         <v>36</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S11" s="1" t="s">
+      <c r="V11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W11" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X11" s="1" t="s">
+      <c r="Y11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="AA11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC11" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC11" s="1" t="s">
+      <c r="AD11" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD11" s="1" t="s">
+      <c r="AE11" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI11" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF11" s="1" t="s">
+      <c r="AJ11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK11" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AG11" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH11" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI11" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AK11" s="1" t="s">
-        <v>113</v>
-      </c>
     </row>
-    <row customFormat="1" r="12" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="12" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
         <v>272</v>
@@ -4466,31 +4416,31 @@
         <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>35</v>
@@ -4499,69 +4449,69 @@
         <v>36</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S12" s="1" t="s">
+      <c r="V12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W12" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W12" s="1" t="s">
+      <c r="X12" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="AA12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC12" s="1" t="s">
+      <c r="AD12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD12" s="1" t="s">
+      <c r="AE12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI12" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE12" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF12" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI12" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ12" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
-    <row customFormat="1" r="13" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="13" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
         <v>273</v>
@@ -4570,31 +4520,31 @@
         <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>35</v>
@@ -4603,69 +4553,69 @@
         <v>36</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S13" s="1" t="s">
+      <c r="V13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W13" s="1" t="s">
+      <c r="X13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X13" s="1" t="s">
+      <c r="Y13" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y13" s="1" t="s">
+      <c r="Z13" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z13" s="1" t="s">
+      <c r="AA13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC13" s="1" t="s">
+      <c r="AD13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD13" s="1" t="s">
+      <c r="AE13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF13" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI13" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF13" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG13" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH13" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI13" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
-    <row customFormat="1" r="14" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="14" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s">
         <v>274</v>
@@ -4674,31 +4624,31 @@
         <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K14" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>35</v>
@@ -4707,69 +4657,69 @@
         <v>36</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S14" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S14" s="1" t="s">
+      <c r="V14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W14" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W14" s="1" t="s">
+      <c r="X14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X14" s="1" t="s">
+      <c r="Y14" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y14" s="1" t="s">
+      <c r="Z14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z14" s="1" t="s">
+      <c r="AA14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC14" s="1" t="s">
+      <c r="AD14" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD14" s="1" t="s">
+      <c r="AE14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI14" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG14" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH14" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI14" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ14" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AK14" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
-    <row customFormat="1" r="15" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="15" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s">
         <v>275</v>
@@ -4778,31 +4728,31 @@
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>35</v>
@@ -4811,69 +4761,69 @@
         <v>36</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S15" s="1" t="s">
+      <c r="V15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W15" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W15" s="1" t="s">
+      <c r="X15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X15" s="1" t="s">
+      <c r="Y15" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y15" s="1" t="s">
+      <c r="Z15" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z15" s="1" t="s">
+      <c r="AA15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC15" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC15" s="1" t="s">
+      <c r="AD15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD15" s="1" t="s">
+      <c r="AE15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI15" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ15" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
-    <row customFormat="1" r="16" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="16" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
         <v>276</v>
@@ -4882,31 +4832,31 @@
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>35</v>
@@ -4915,69 +4865,69 @@
         <v>36</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S16" s="1" t="s">
+      <c r="V16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W16" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W16" s="1" t="s">
+      <c r="X16" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X16" s="1" t="s">
+      <c r="Y16" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z16" s="1" t="s">
+      <c r="AA16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC16" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AD16" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD16" s="1" t="s">
+      <c r="AE16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI16" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF16" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG16" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH16" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI16" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
-    <row customFormat="1" r="17" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="17" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
         <v>277</v>
@@ -4986,31 +4936,31 @@
         <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>35</v>
@@ -5019,69 +4969,69 @@
         <v>36</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S17" s="1" t="s">
+      <c r="V17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W17" s="1" t="s">
+      <c r="X17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X17" s="1" t="s">
+      <c r="Y17" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y17" s="1" t="s">
+      <c r="Z17" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z17" s="1" t="s">
+      <c r="AA17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC17" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC17" s="1" t="s">
+      <c r="AD17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD17" s="1" t="s">
+      <c r="AE17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG17" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI17" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE17" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH17" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI17" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
-    <row customFormat="1" r="18" s="1" spans="1:37" x14ac:dyDescent="0.35">
+    <row customFormat="1" r="18" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
         <v>278</v>
@@ -5090,31 +5040,31 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>35</v>
@@ -5123,105 +5073,105 @@
         <v>36</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S18" s="1" t="s">
+      <c r="V18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W18" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="V18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W18" s="1" t="s">
+      <c r="X18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X18" s="1" t="s">
+      <c r="Y18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y18" s="1" t="s">
+      <c r="Z18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z18" s="1" t="s">
+      <c r="AA18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC18" s="1" t="s">
+      <c r="AD18" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD18" s="1" t="s">
+      <c r="AE18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE18" s="1" t="s">
+      <c r="AJ18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AK18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="AF18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG18" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH18" s="1" t="s">
+    </row>
+    <row customFormat="1" ht="28.5" r="19" s="1" spans="1:37" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AI18" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AK18" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row customFormat="1" ht="29" r="19" s="1" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" t="s">
-        <v>221</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>35</v>
@@ -5230,70 +5180,71 @@
         <v>36</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="Q19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S19" s="1" t="s">
+      <c r="U19" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W19" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="U19" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W19" s="1" t="s">
+      <c r="X19" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="X19" s="1" t="s">
+      <c r="Y19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Y19" s="1" t="s">
+      <c r="Z19" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z19" s="1" t="s">
+      <c r="AA19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC19" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AA19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC19" s="1" t="s">
+      <c r="AD19" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AD19" s="1" t="s">
+      <c r="AE19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AI19" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="AE19" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AG19" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AH19" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AI19" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="AJ19" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
   <headerFooter>
@@ -5305,48 +5256,48 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84AF6F86-8ED4-4308-B6F8-71B93F250506}">
   <dimension ref="A1:AK19"/>
-  <sheetFormatPr defaultColWidth="50.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="50.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.81640625" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.796875" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="22.26953125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="28.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="32.54296875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.1796875" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="19.453125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="8.26953125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="1" width="33.1796875" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" style="1" width="19.453125" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="22.265625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="28.73046875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="32.53125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.19921875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="19.46484375" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="8.265625" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="1" width="33.19921875" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="1" width="19.46484375" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="15.53125" collapsed="true"/>
     <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="12.453125" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="42.453125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="14.7265625" collapsed="true"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="8.81640625" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="15.1796875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="10.81640625" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="12.46484375" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="42.46484375" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="10.796875" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="20.7265625" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="13.453125" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.54296875" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="20.73046875" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="13.46484375" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.53125" collapsed="true"/>
     <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="17.7265625" collapsed="true"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="5.453125" collapsed="true"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="2" width="16.81640625" collapsed="true"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" style="2" width="25.54296875" collapsed="true"/>
-    <col min="37" max="16384" style="1" width="50.54296875" collapsed="true"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="17.73046875" collapsed="true"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="5.46484375" collapsed="true"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="2" width="16.796875" collapsed="true"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" style="2" width="25.53125" collapsed="true"/>
+    <col min="37" max="16384" style="1" width="50.53125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5360,28 +5311,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="K1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>12</v>
@@ -5393,22 +5344,22 @@
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>17</v>
@@ -5444,60 +5395,60 @@
         <v>27</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="M2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -5508,409 +5459,409 @@
         <v>256072691</v>
       </c>
       <c r="T2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="V2" s="3">
         <v>11.5</v>
       </c>
       <c r="W2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG2" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AJ2" s="1"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K3" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="M3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S3" s="3">
         <v>256072691</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V3" s="3">
         <v>11.5</v>
       </c>
       <c r="W3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y3" s="3" t="s">
+      <c r="AA3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG3" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AJ3" s="1"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K4" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="O4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S4" s="3">
         <v>256072691</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V4" s="3">
         <v>11.5</v>
       </c>
       <c r="W4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y4" s="3" t="s">
+      <c r="AA4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF4" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG4" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S5" s="3">
         <v>256072691</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V5" s="3">
         <v>11.5</v>
       </c>
       <c r="W5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y5" s="3" t="s">
+      <c r="AA5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="3" t="s">
+      <c r="AC5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC5" s="3" t="s">
+      <c r="AE5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF5" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG5" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AJ5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="M6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -5921,408 +5872,408 @@
         <v>256072691</v>
       </c>
       <c r="T6" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="U6" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="V6" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="W6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y6" s="3" t="s">
+      <c r="AA6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA6" s="3" t="s">
+      <c r="AC6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC6" s="3" t="s">
+      <c r="AE6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG6" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AI6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="M7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S7" s="3">
         <v>256072691</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V7" s="3">
         <v>11.5</v>
       </c>
       <c r="W7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y7" s="3" t="s">
+      <c r="AA7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA7" s="3" t="s">
+      <c r="AC7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC7" s="3" t="s">
+      <c r="AE7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG7" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K8" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="O8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S8" s="3">
         <v>256072691</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V8" s="3">
         <v>11.5</v>
       </c>
       <c r="W8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AC8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC8" s="3" t="s">
+      <c r="AE8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG8" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S9" s="3">
         <v>256072691</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V9" s="3">
         <v>11.5</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA9" s="3" t="s">
+      <c r="AC9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC9" s="3" t="s">
+      <c r="AE9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF9" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG9" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K10" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="M10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -6333,408 +6284,408 @@
         <v>256072691</v>
       </c>
       <c r="T10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="V10" s="3">
         <v>11.5</v>
       </c>
       <c r="W10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y10" s="3" t="s">
+      <c r="AA10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA10" s="3" t="s">
+      <c r="AC10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC10" s="3" t="s">
+      <c r="AE10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF10" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG10" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="M11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N11" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S11" s="3">
         <v>256072691</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V11" s="3">
         <v>11.5</v>
       </c>
       <c r="W11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="AA11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC11" s="3" t="s">
+      <c r="AE11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF11" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG11" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="O12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S12" s="3">
         <v>256072691</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V12" s="3">
         <v>11.5</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA12" s="3" t="s">
+      <c r="AC12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC12" s="3" t="s">
+      <c r="AE12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF12" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG12" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K13" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="N13" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O13" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S13" s="3">
         <v>256072691</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V13" s="3">
         <v>11.5</v>
       </c>
       <c r="W13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y13" s="3" t="s">
+      <c r="AA13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA13" s="3" t="s">
+      <c r="AC13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC13" s="3" t="s">
+      <c r="AE13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF13" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG13" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K14" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="M14" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -6745,408 +6696,408 @@
         <v>256072691</v>
       </c>
       <c r="T14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="V14" s="3">
         <v>11.5</v>
       </c>
       <c r="W14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG14" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="M15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O15" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S15" s="3">
         <v>256072691</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V15" s="3">
         <v>11.5</v>
       </c>
       <c r="W15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y15" s="3" t="s">
+      <c r="AA15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA15" s="3" t="s">
+      <c r="AC15" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="AD15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="AE15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="O16" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="S16" s="3">
         <v>256072691</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="V16" s="3">
         <v>11.5</v>
       </c>
       <c r="W16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y16" s="3" t="s">
+      <c r="AA16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB16" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="AC16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD16" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF16" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG16" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="N17" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="O17" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="S17" s="3">
         <v>256072691</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V17" s="3">
         <v>11.5</v>
       </c>
       <c r="W17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y17" s="3" t="s">
+      <c r="AA17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA17" s="3" t="s">
+      <c r="AC17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC17" s="3" t="s">
+      <c r="AE17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE17" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="AF17" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG17" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="K18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="M18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N18" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -7157,163 +7108,163 @@
         <v>256072691</v>
       </c>
       <c r="T18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="V18" s="3">
         <v>11.5</v>
       </c>
       <c r="W18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y18" s="3" t="s">
+      <c r="AA18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA18" s="3" t="s">
+      <c r="AC18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD18" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="AE18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AH18" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row ht="28.5" r="19" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AI18" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row ht="29" r="19" spans="1:36" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="M19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S19" s="3">
         <v>256072691</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V19" s="3">
         <v>11.5</v>
       </c>
       <c r="W19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y19" s="3" t="s">
+      <c r="AA19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA19" s="3" t="s">
+      <c r="AC19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC19" s="3" t="s">
+      <c r="AE19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF19" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AG19" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -7324,46 +7275,46 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E68805-B27C-428C-BFE2-4FA9EF8F5B1E}">
   <dimension ref="A1:AI3"/>
-  <sheetFormatPr defaultColWidth="50.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="50.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.1796875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.19921875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="6.265625" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="22.26953125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="28.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="32.54296875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.1796875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="15.1796875" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="19.453125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="8.26953125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="13.1796875" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="14.1796875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="22.265625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="28.73046875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="32.53125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.19921875" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="19.46484375" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="8.265625" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="13.19921875" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="15.53125" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="1" width="15.53125" collapsed="true"/>
     <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="12.453125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="42.453125" collapsed="true"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="12.46484375" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="42.46484375" collapsed="true"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
     <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.81640625" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="7.26953125" collapsed="true"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="7.265625" collapsed="true"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
     <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
     <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.81640625" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="6.81640625" collapsed="true"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="11.453125" collapsed="true"/>
-    <col min="34" max="34" customWidth="true" style="1" width="74.453125" collapsed="true"/>
-    <col min="35" max="16384" style="1" width="50.54296875" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="7.796875" collapsed="true"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="6.796875" collapsed="true"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
+    <col min="34" max="34" customWidth="true" style="1" width="74.46484375" collapsed="true"/>
+    <col min="35" max="16384" style="1" width="50.53125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7377,28 +7328,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="K1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>12</v>
@@ -7410,25 +7361,25 @@
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>17</v>
@@ -7464,33 +7415,33 @@
         <v>27</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="M2" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -7502,125 +7453,125 @@
         <v>256072691</v>
       </c>
       <c r="U2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="W2" s="3">
         <v>11.5</v>
       </c>
       <c r="X2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AA2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AD2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AC2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AE2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AH2" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
-    <row ht="29" r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row ht="28.5" r="3" spans="1:34" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="M3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="O3" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="T3" s="3">
         <v>256072691</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W3" s="3">
         <v>11.5</v>
       </c>
       <c r="X3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z3" s="3" t="s">
+      <c r="AB3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AA3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AE3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="AH3" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -7634,44 +7585,44 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9839FF8-C1B0-4ABF-93FF-3EB28089C08C}">
   <dimension ref="A1:AG2"/>
-  <sheetFormatPr defaultColWidth="50.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="50.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.1796875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="5.19921875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="6.265625" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="22.26953125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="28.7265625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="32.54296875" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.1796875" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.7265625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="19.453125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="8.26953125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="1" width="10.54296875" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="13.1796875" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="14.1796875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="22.265625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="11.73046875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="28.73046875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="32.53125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.19921875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="9.73046875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="19.46484375" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="8.265625" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="1" width="10.53125" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="13.19921875" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="15.53125" collapsed="true"/>
     <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="12.453125" collapsed="true"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="42.453125" collapsed="true"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="12.46484375" collapsed="true"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="42.46484375" collapsed="true"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
     <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.0" collapsed="true"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="8.81640625" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="7.26953125" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="8.1796875" collapsed="true"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="8.796875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="7.265625" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="8.19921875" collapsed="true"/>
     <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="7.0" collapsed="true"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="7.46484375" collapsed="true"/>
     <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="12.0" collapsed="true"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="7.81640625" collapsed="true"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="6.81640625" collapsed="true"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="11.453125" collapsed="true"/>
-    <col min="33" max="16384" style="1" width="50.54296875" collapsed="true"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="7.796875" collapsed="true"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="6.796875" collapsed="true"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="11.46484375" collapsed="true"/>
+    <col min="33" max="16384" style="1" width="50.53125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7685,28 +7636,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="K1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>12</v>
@@ -7718,22 +7669,22 @@
         <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="V1" s="3" t="s">
         <v>17</v>
@@ -7769,75 +7720,75 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="K2" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S2" s="3">
         <v>256072691</v>
       </c>
       <c r="T2" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="V2" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="W2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AB2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF2" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -7851,20 +7802,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58603BCF-4622-4E65-9487-561DE995DE00}">
   <dimension ref="A1:AC3"/>
-  <sheetFormatPr defaultColWidth="12.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="4" style="1" width="12.1796875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="32.26953125" collapsed="true"/>
+    <col min="1" max="4" style="1" width="12.19921875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.46484375" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="32.265625" collapsed="true"/>
     <col min="7" max="7" customWidth="true" style="1" width="22.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="30.54296875" collapsed="true"/>
-    <col min="10" max="12" style="1" width="12.1796875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="24.453125" collapsed="true"/>
-    <col min="14" max="16384" style="1" width="12.1796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="15.53125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="30.53125" collapsed="true"/>
+    <col min="10" max="12" style="1" width="12.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="12.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7950,18 +7901,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>33</v>
@@ -7976,63 +7927,63 @@
         <v>36</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="S2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>51</v>
-      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="D3" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>34</v>
@@ -8044,46 +7995,46 @@
         <v>36</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>260</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="S3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/Bootstrap/VT-Misc-Data.xlsx
+++ b/KatalonData/Bootstrap/VT-Misc-Data.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="381">
   <si>
     <t>Result</t>
   </si>
@@ -881,6 +881,312 @@
   </si>
   <si>
     <t>Tue Jan 20 20:06:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:46:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:47:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:48:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:49:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:49:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:50:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:51:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:52:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:53:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:53:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:54:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:55:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:56:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:57:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:57:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:58:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 17:59:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:00:20 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:01:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:02:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:03:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:03:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:04:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:05:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:06:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:07:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:08:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:09:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:10:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:11:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:12:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:12:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:13:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 18:14:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:43:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:44:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:45:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:46:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:47:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:48:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:49:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:51:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:52:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:53:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:54:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:55:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:56:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:57:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:58:33 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 16:59:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:00:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:01:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:02:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:03:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:04:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:06:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:07:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:08:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:09:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:10:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:11:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:12:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:13:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:14:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:15:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:16:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:17:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:18:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:19:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:20:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:21:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:22:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:23:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:24:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:25:53 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:26:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:28:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:29:12 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:30:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:31:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:32:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:33:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:34:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:35:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:36:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:37:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:38:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:39:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:41:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:42:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:43:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:44:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:45:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:46:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:47:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:48:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:49:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:50:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:51:38 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:52:43 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:53:45 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 17:54:46 EST 2026</t>
   </si>
 </sst>
 </file>
@@ -3373,7 +3679,7 @@
         <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>364</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>31</v>
@@ -3471,10 +3777,10 @@
     </row>
     <row customFormat="1" r="3" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>31</v>
@@ -3575,7 +3881,7 @@
         <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>366</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>31</v>
@@ -3679,7 +3985,7 @@
         <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>367</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>31</v>
@@ -3786,7 +4092,7 @@
         <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>368</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>31</v>
@@ -3890,7 +4196,7 @@
         <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>369</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>31</v>
@@ -3994,7 +4300,7 @@
         <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>370</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>31</v>
@@ -4098,7 +4404,7 @@
         <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>371</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>31</v>
@@ -4202,7 +4508,7 @@
         <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>372</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>31</v>
@@ -4306,7 +4612,7 @@
         <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>373</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>31</v>
@@ -4410,7 +4716,7 @@
         <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>374</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>31</v>
@@ -4514,7 +4820,7 @@
         <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>375</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>31</v>
@@ -4618,7 +4924,7 @@
         <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>376</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>31</v>
@@ -4722,7 +5028,7 @@
         <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>377</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>31</v>
@@ -4826,7 +5132,7 @@
         <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>31</v>
@@ -4930,7 +5236,7 @@
         <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>379</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>31</v>
@@ -5034,7 +5340,7 @@
         <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>380</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>31</v>
@@ -5412,7 +5718,7 @@
         <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>31</v>
@@ -5513,7 +5819,7 @@
         <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>297</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>31</v>
@@ -5614,7 +5920,7 @@
         <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>217</v>
@@ -5720,7 +6026,7 @@
         <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>299</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>31</v>
@@ -5825,7 +6131,7 @@
         <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>31</v>
@@ -5928,7 +6234,7 @@
         <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>248</v>
+        <v>301</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>31</v>
@@ -6031,7 +6337,7 @@
         <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>31</v>
@@ -6134,7 +6440,7 @@
         <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>303</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>31</v>
@@ -6237,7 +6543,7 @@
         <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>304</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>31</v>
@@ -6340,7 +6646,7 @@
         <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
+        <v>305</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>31</v>
@@ -6443,7 +6749,7 @@
         <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>253</v>
+        <v>306</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>31</v>
@@ -6546,7 +6852,7 @@
         <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>31</v>
@@ -6649,7 +6955,7 @@
         <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>31</v>
@@ -6752,7 +7058,7 @@
         <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>309</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>31</v>
@@ -6855,7 +7161,7 @@
         <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>31</v>
@@ -6958,7 +7264,7 @@
         <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>31</v>
@@ -7061,7 +7367,7 @@
         <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>31</v>

--- a/KatalonData/Bootstrap/VT-Misc-Data.xlsx
+++ b/KatalonData/Bootstrap/VT-Misc-Data.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2085" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="344">
   <si>
     <t>Result</t>
   </si>
@@ -881,6 +881,201 @@
   </si>
   <si>
     <t>Tue Jan 20 20:06:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:24:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:27:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:28:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:30:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:31:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:33:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:35:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:36:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:38:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:40:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:41:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:43:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:45:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:46:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:48:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:51:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:53:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 22:54:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:00:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:01:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:02:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:04:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:05:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:07:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:08:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:10:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:12:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:14:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:15:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:17:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:19:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:20:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:22:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:24:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:25:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:27:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:29:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:30:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:32:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:34:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:36:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:37:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:39:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:42:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:44:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:46:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:48:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:49:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:52:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 20 23:54:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:26:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:28:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:29:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:31:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:32:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:34:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:37:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:38:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:40:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:42:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 22 19:43:22 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -3373,7 +3568,7 @@
         <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>332</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>31</v>
@@ -3471,10 +3666,10 @@
     </row>
     <row customFormat="1" r="3" s="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="B3" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>31</v>
@@ -3575,7 +3770,7 @@
         <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>31</v>
@@ -3679,7 +3874,7 @@
         <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>31</v>
@@ -3786,7 +3981,7 @@
         <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>31</v>
@@ -3890,7 +4085,7 @@
         <v>175</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>31</v>
@@ -3994,7 +4189,7 @@
         <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>31</v>
@@ -4098,7 +4293,7 @@
         <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>31</v>
@@ -4202,7 +4397,7 @@
         <v>175</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>31</v>
@@ -4306,7 +4501,7 @@
         <v>175</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>31</v>
@@ -4410,7 +4605,7 @@
         <v>175</v>
       </c>
       <c r="B12" t="s">
-        <v>272</v>
+        <v>342</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>31</v>
@@ -4514,7 +4709,7 @@
         <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>31</v>
@@ -4618,7 +4813,7 @@
         <v>175</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>31</v>
@@ -4722,7 +4917,7 @@
         <v>175</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>31</v>
@@ -4826,7 +5021,7 @@
         <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>31</v>
@@ -4930,7 +5125,7 @@
         <v>175</v>
       </c>
       <c r="B17" t="s">
-        <v>277</v>
+        <v>330</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>31</v>
@@ -5034,7 +5229,7 @@
         <v>175</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>31</v>
